--- a/dataAcquisition/Motec_MP/alias/eventAlias.xlsx
+++ b/dataAcquisition/Motec_MP/alias/eventAlias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SimEnv\dataAcquisition\Motec_MP\alias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA728DC-B2E1-4A36-ACB3-8D485998E3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020A04CF-7EB6-4C9F-8DA3-FCD7FF209789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1935" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{968229EC-9479-47A1-8BEC-6418C2655BFD}"/>
+    <workbookView xWindow="28680" yWindow="735" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{968229EC-9479-47A1-8BEC-6418C2655BFD}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENT" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="357">
   <si>
     <t>V8SC_Name</t>
   </si>
@@ -1097,6 +1097,18 @@
   </si>
   <si>
     <t>Qualifying Race 9</t>
+  </si>
+  <si>
+    <t>Run 16</t>
+  </si>
+  <si>
+    <t>Run 14</t>
+  </si>
+  <si>
+    <t>T02</t>
+  </si>
+  <si>
+    <t>AT1 - QR</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1489,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -1748,6 +1760,71 @@
         <v>21</v>
       </c>
       <c r="U4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+      <c r="T5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2260,10 +2337,10 @@
         <v>322</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
